--- a/public/Template.xlsx
+++ b/public/Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jorda\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48EFE8D8-AB3C-4C6A-A680-57C9EABC52FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E32DA42-FC54-4F25-8F7B-244F758A5D9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="July 2025 Summary" sheetId="7" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="292">
   <si>
     <t xml:space="preserve">Consignment Extract </t>
   </si>
@@ -904,6 +904,15 @@
   </si>
   <si>
     <t>Pickup From:    31 Jul 2025      To:  31 Jul 2025</t>
+  </si>
+  <si>
+    <t>WW</t>
+  </si>
+  <si>
+    <t>FS CHC</t>
+  </si>
+  <si>
+    <t>FS DUD</t>
   </si>
 </sst>
 </file>
@@ -1241,7 +1250,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1337,6 +1346,9 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1377,10 +1389,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1801,7 +1816,7 @@
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
-      <c r="K2" s="62" t="s">
+      <c r="K2" s="65" t="s">
         <v>66</v>
       </c>
       <c r="L2" s="2"/>
@@ -1811,7 +1826,7 @@
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
       <c r="R2" s="2"/>
-      <c r="S2" s="62" t="s">
+      <c r="S2" s="65" t="s">
         <v>71</v>
       </c>
       <c r="T2" s="18"/>
@@ -1821,7 +1836,7 @@
       <c r="X2" s="2"/>
       <c r="Y2" s="2"/>
       <c r="Z2" s="2"/>
-      <c r="AA2" s="62" t="s">
+      <c r="AA2" s="65" t="s">
         <v>72</v>
       </c>
       <c r="AB2" s="18"/>
@@ -1831,7 +1846,7 @@
       <c r="AF2" s="2"/>
       <c r="AG2" s="2"/>
       <c r="AH2" s="2"/>
-      <c r="AI2" s="62" t="s">
+      <c r="AI2" s="65" t="s">
         <v>73</v>
       </c>
       <c r="AJ2" s="2"/>
@@ -1840,10 +1855,10 @@
       <c r="AM2" s="2"/>
       <c r="AN2" s="2"/>
       <c r="AO2" s="2"/>
-      <c r="AP2" s="58" t="s">
+      <c r="AP2" s="61" t="s">
         <v>74</v>
       </c>
-      <c r="AR2" s="56" t="s">
+      <c r="AR2" s="59" t="s">
         <v>75</v>
       </c>
     </row>
@@ -1857,7 +1872,7 @@
       <c r="H3" s="25"/>
       <c r="I3" s="25"/>
       <c r="J3" s="25"/>
-      <c r="K3" s="63"/>
+      <c r="K3" s="66"/>
       <c r="L3" s="25"/>
       <c r="M3" s="25"/>
       <c r="N3" s="25"/>
@@ -1865,7 +1880,7 @@
       <c r="P3" s="25"/>
       <c r="Q3" s="25"/>
       <c r="R3" s="25"/>
-      <c r="S3" s="63"/>
+      <c r="S3" s="66"/>
       <c r="T3" s="18"/>
       <c r="U3" s="25"/>
       <c r="V3" s="25"/>
@@ -1873,7 +1888,7 @@
       <c r="X3" s="25"/>
       <c r="Y3" s="25"/>
       <c r="Z3" s="25"/>
-      <c r="AA3" s="63"/>
+      <c r="AA3" s="66"/>
       <c r="AB3" s="18"/>
       <c r="AC3" s="25"/>
       <c r="AD3" s="25"/>
@@ -1881,15 +1896,15 @@
       <c r="AF3" s="25"/>
       <c r="AG3" s="25"/>
       <c r="AH3" s="25"/>
-      <c r="AI3" s="63"/>
+      <c r="AI3" s="66"/>
       <c r="AJ3" s="25"/>
       <c r="AK3" s="25"/>
       <c r="AL3" s="25"/>
       <c r="AM3" s="25"/>
       <c r="AN3" s="25"/>
       <c r="AO3" s="25"/>
-      <c r="AP3" s="60"/>
-      <c r="AR3" s="57"/>
+      <c r="AP3" s="63"/>
+      <c r="AR3" s="60"/>
     </row>
     <row r="4" spans="2:46" ht="4.1500000000000004" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E4" s="2"/>
@@ -1931,7 +1946,7 @@
       <c r="AO4" s="2"/>
     </row>
     <row r="5" spans="2:46" ht="14.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="58" t="s">
+      <c r="B5" s="61" t="s">
         <v>62</v>
       </c>
       <c r="C5" s="45" t="s">
@@ -1939,7 +1954,7 @@
       </c>
       <c r="D5" s="53"/>
       <c r="E5" s="27"/>
-      <c r="F5" s="69"/>
+      <c r="F5" s="55"/>
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
       <c r="I5" s="5"/>
@@ -1989,13 +2004,13 @@
       </c>
     </row>
     <row r="6" spans="2:46" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="59"/>
+      <c r="B6" s="62"/>
       <c r="C6" s="45" t="s">
         <v>59</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="28"/>
-      <c r="F6" s="70"/>
+      <c r="F6" s="3"/>
       <c r="I6" s="6"/>
       <c r="K6" s="16">
         <f>SUM(E6:I6)</f>
@@ -2030,13 +2045,13 @@
       </c>
     </row>
     <row r="7" spans="2:46" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="59"/>
+      <c r="B7" s="62"/>
       <c r="C7" s="45" t="s">
         <v>60</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="28"/>
-      <c r="F7" s="70"/>
+      <c r="F7" s="3"/>
       <c r="I7" s="6"/>
       <c r="K7" s="16">
         <f>SUM(E7:I7)</f>
@@ -2071,13 +2086,13 @@
       </c>
     </row>
     <row r="8" spans="2:46" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="60"/>
+      <c r="B8" s="63"/>
       <c r="C8" s="45" t="s">
         <v>61</v>
       </c>
       <c r="D8" s="26"/>
       <c r="E8" s="29"/>
-      <c r="F8" s="71"/>
+      <c r="F8" s="56"/>
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
       <c r="I8" s="8"/>
@@ -2135,7 +2150,7 @@
       <c r="AK9" s="20"/>
     </row>
     <row r="10" spans="2:46" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="58" t="s">
+      <c r="B10" s="61" t="s">
         <v>63</v>
       </c>
       <c r="C10" s="45" t="s">
@@ -2143,7 +2158,7 @@
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="27"/>
-      <c r="F10" s="69"/>
+      <c r="F10" s="55"/>
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
       <c r="I10" s="5"/>
@@ -2192,13 +2207,13 @@
       </c>
     </row>
     <row r="11" spans="2:46" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="59"/>
+      <c r="B11" s="62"/>
       <c r="C11" s="45" t="s">
         <v>59</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="28"/>
-      <c r="F11" s="70"/>
+      <c r="F11" s="3"/>
       <c r="I11" s="6"/>
       <c r="K11" s="16">
         <f>SUM(E11:I11)</f>
@@ -2233,13 +2248,13 @@
       </c>
     </row>
     <row r="12" spans="2:46" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="59"/>
+      <c r="B12" s="62"/>
       <c r="C12" s="45" t="s">
         <v>60</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="28"/>
-      <c r="F12" s="70"/>
+      <c r="F12" s="3"/>
       <c r="I12" s="6"/>
       <c r="K12" s="16">
         <f>SUM(E12:I12)</f>
@@ -2274,13 +2289,13 @@
       </c>
     </row>
     <row r="13" spans="2:46" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="61"/>
+      <c r="B13" s="64"/>
       <c r="C13" s="46" t="s">
         <v>61</v>
       </c>
       <c r="D13" s="26"/>
       <c r="E13" s="47"/>
-      <c r="F13" s="72"/>
+      <c r="F13" s="57"/>
       <c r="G13" s="48"/>
       <c r="H13" s="48"/>
       <c r="I13" s="49"/>
@@ -2336,7 +2351,7 @@
       <c r="F14" s="2"/>
     </row>
     <row r="15" spans="2:46" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="64" t="s">
+      <c r="B15" s="67" t="s">
         <v>89</v>
       </c>
       <c r="C15" s="45" t="s">
@@ -2374,7 +2389,7 @@
       </c>
     </row>
     <row r="16" spans="2:46" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="55"/>
+      <c r="B16" s="58"/>
       <c r="C16" s="45" t="s">
         <v>59</v>
       </c>
@@ -2410,7 +2425,7 @@
       </c>
     </row>
     <row r="17" spans="2:46" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="55"/>
+      <c r="B17" s="58"/>
       <c r="C17" s="45" t="s">
         <v>60</v>
       </c>
@@ -2446,7 +2461,7 @@
       </c>
     </row>
     <row r="18" spans="2:46" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="55"/>
+      <c r="B18" s="58"/>
       <c r="C18" s="45" t="s">
         <v>61</v>
       </c>
@@ -2535,7 +2550,7 @@
       <c r="AR21" s="31"/>
     </row>
     <row r="22" spans="2:46" s="24" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="55" t="s">
+      <c r="B22" s="58" t="s">
         <v>90</v>
       </c>
       <c r="C22" s="32" t="s">
@@ -2572,7 +2587,7 @@
       </c>
     </row>
     <row r="23" spans="2:46" s="24" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="55"/>
+      <c r="B23" s="58"/>
       <c r="C23" s="32" t="s">
         <v>83</v>
       </c>
@@ -2607,7 +2622,7 @@
       </c>
     </row>
     <row r="24" spans="2:46" s="24" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="55"/>
+      <c r="B24" s="58"/>
       <c r="C24" s="32" t="s">
         <v>59</v>
       </c>
@@ -2642,7 +2657,7 @@
       </c>
     </row>
     <row r="25" spans="2:46" s="24" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="55"/>
+      <c r="B25" s="58"/>
       <c r="C25" s="32" t="s">
         <v>60</v>
       </c>
@@ -2677,7 +2692,7 @@
       </c>
     </row>
     <row r="26" spans="2:46" s="24" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="55"/>
+      <c r="B26" s="58"/>
       <c r="C26" s="32" t="s">
         <v>61</v>
       </c>
@@ -2724,22 +2739,109 @@
       <c r="F28" s="2"/>
     </row>
     <row r="29" spans="2:46" x14ac:dyDescent="0.25">
-      <c r="C29" s="25"/>
+      <c r="C29" s="1" t="s">
+        <v>289</v>
+      </c>
       <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
+      <c r="E29" s="76"/>
+      <c r="F29" s="77"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="5"/>
+      <c r="K29" s="74"/>
+      <c r="M29" s="13"/>
+      <c r="N29" s="4"/>
+      <c r="O29" s="4"/>
+      <c r="P29" s="4"/>
+      <c r="Q29" s="5"/>
+      <c r="S29" s="74"/>
+      <c r="U29" s="13"/>
+      <c r="V29" s="4"/>
+      <c r="W29" s="4"/>
+      <c r="X29" s="4"/>
+      <c r="Y29" s="5"/>
+      <c r="AA29" s="74"/>
+      <c r="AC29" s="13"/>
+      <c r="AD29" s="4"/>
+      <c r="AE29" s="4"/>
+      <c r="AF29" s="4"/>
+      <c r="AG29" s="5"/>
+      <c r="AI29" s="74"/>
+      <c r="AK29" s="13"/>
+      <c r="AL29" s="4"/>
+      <c r="AM29" s="4"/>
+      <c r="AN29" s="5"/>
+      <c r="AP29" s="74"/>
     </row>
     <row r="30" spans="2:46" x14ac:dyDescent="0.25">
-      <c r="C30" s="25"/>
+      <c r="C30" s="1" t="s">
+        <v>291</v>
+      </c>
       <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="72"/>
+      <c r="G30" s="73"/>
+      <c r="H30" s="73"/>
+      <c r="I30" s="6"/>
+      <c r="K30" s="11"/>
+      <c r="M30" s="12"/>
+      <c r="N30" s="73"/>
+      <c r="O30" s="73"/>
+      <c r="P30" s="73"/>
+      <c r="Q30" s="6"/>
+      <c r="S30" s="11"/>
+      <c r="U30" s="12"/>
+      <c r="V30" s="73"/>
+      <c r="W30" s="73"/>
+      <c r="X30" s="73"/>
+      <c r="Y30" s="6"/>
+      <c r="AA30" s="11"/>
+      <c r="AC30" s="12"/>
+      <c r="AD30" s="73"/>
+      <c r="AE30" s="73"/>
+      <c r="AF30" s="73"/>
+      <c r="AG30" s="6"/>
+      <c r="AI30" s="11"/>
+      <c r="AK30" s="12"/>
+      <c r="AL30" s="73"/>
+      <c r="AM30" s="73"/>
+      <c r="AN30" s="6"/>
+      <c r="AP30" s="11"/>
     </row>
     <row r="31" spans="2:46" x14ac:dyDescent="0.25">
-      <c r="C31" s="25"/>
+      <c r="C31" s="1" t="s">
+        <v>290</v>
+      </c>
       <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
+      <c r="E31" s="78"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="7"/>
+      <c r="H31" s="7"/>
+      <c r="I31" s="8"/>
+      <c r="K31" s="75"/>
+      <c r="M31" s="14"/>
+      <c r="N31" s="7"/>
+      <c r="O31" s="7"/>
+      <c r="P31" s="7"/>
+      <c r="Q31" s="8"/>
+      <c r="S31" s="75"/>
+      <c r="U31" s="14"/>
+      <c r="V31" s="7"/>
+      <c r="W31" s="7"/>
+      <c r="X31" s="7"/>
+      <c r="Y31" s="8"/>
+      <c r="AA31" s="75"/>
+      <c r="AC31" s="14"/>
+      <c r="AD31" s="7"/>
+      <c r="AE31" s="7"/>
+      <c r="AF31" s="7"/>
+      <c r="AG31" s="8"/>
+      <c r="AI31" s="75"/>
+      <c r="AK31" s="14"/>
+      <c r="AL31" s="7"/>
+      <c r="AM31" s="7"/>
+      <c r="AN31" s="8"/>
+      <c r="AP31" s="75"/>
     </row>
     <row r="32" spans="2:46" x14ac:dyDescent="0.25">
       <c r="C32" s="25"/>
@@ -2820,135 +2922,135 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="66"/>
-      <c r="H1" s="66"/>
-      <c r="I1" s="66"/>
-      <c r="J1" s="66"/>
-      <c r="K1" s="66"/>
-      <c r="L1" s="66"/>
-      <c r="M1" s="66"/>
-      <c r="N1" s="66"/>
-      <c r="O1" s="66"/>
-      <c r="P1" s="66"/>
-      <c r="Q1" s="66"/>
-      <c r="R1" s="66"/>
-      <c r="S1" s="66"/>
-      <c r="T1" s="66"/>
-      <c r="U1" s="66"/>
-      <c r="V1" s="66"/>
+      <c r="A1" s="68" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="69"/>
+      <c r="I1" s="69"/>
+      <c r="J1" s="69"/>
+      <c r="K1" s="69"/>
+      <c r="L1" s="69"/>
+      <c r="M1" s="69"/>
+      <c r="N1" s="69"/>
+      <c r="O1" s="69"/>
+      <c r="P1" s="69"/>
+      <c r="Q1" s="69"/>
+      <c r="R1" s="69"/>
+      <c r="S1" s="69"/>
+      <c r="T1" s="69"/>
+      <c r="U1" s="69"/>
+      <c r="V1" s="69"/>
     </row>
     <row r="2" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="67" t="s">
+      <c r="A2" s="70" t="s">
         <v>173</v>
       </c>
-      <c r="B2" s="66"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="66"/>
-      <c r="H2" s="66"/>
-      <c r="I2" s="66"/>
-      <c r="J2" s="66"/>
-      <c r="K2" s="66"/>
-      <c r="L2" s="66"/>
-      <c r="M2" s="66"/>
-      <c r="N2" s="66"/>
-      <c r="O2" s="66"/>
-      <c r="P2" s="66"/>
-      <c r="Q2" s="66"/>
-      <c r="R2" s="66"/>
-      <c r="S2" s="66"/>
-      <c r="T2" s="66"/>
-      <c r="U2" s="66"/>
-      <c r="V2" s="66"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="69"/>
+      <c r="L2" s="69"/>
+      <c r="M2" s="69"/>
+      <c r="N2" s="69"/>
+      <c r="O2" s="69"/>
+      <c r="P2" s="69"/>
+      <c r="Q2" s="69"/>
+      <c r="R2" s="69"/>
+      <c r="S2" s="69"/>
+      <c r="T2" s="69"/>
+      <c r="U2" s="69"/>
+      <c r="V2" s="69"/>
     </row>
     <row r="3" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="68" t="s">
+      <c r="A3" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="66"/>
-      <c r="C3" s="66"/>
-      <c r="D3" s="66"/>
-      <c r="E3" s="66"/>
-      <c r="F3" s="66"/>
-      <c r="G3" s="66"/>
-      <c r="H3" s="66"/>
-      <c r="I3" s="66"/>
-      <c r="J3" s="66"/>
-      <c r="K3" s="66"/>
-      <c r="L3" s="66"/>
-      <c r="M3" s="66"/>
-      <c r="N3" s="66"/>
-      <c r="O3" s="66"/>
-      <c r="P3" s="66"/>
-      <c r="Q3" s="66"/>
-      <c r="R3" s="66"/>
-      <c r="S3" s="66"/>
-      <c r="T3" s="66"/>
-      <c r="U3" s="66"/>
-      <c r="V3" s="66"/>
+      <c r="B3" s="69"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="69"/>
+      <c r="F3" s="69"/>
+      <c r="G3" s="69"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="69"/>
+      <c r="J3" s="69"/>
+      <c r="K3" s="69"/>
+      <c r="L3" s="69"/>
+      <c r="M3" s="69"/>
+      <c r="N3" s="69"/>
+      <c r="O3" s="69"/>
+      <c r="P3" s="69"/>
+      <c r="Q3" s="69"/>
+      <c r="R3" s="69"/>
+      <c r="S3" s="69"/>
+      <c r="T3" s="69"/>
+      <c r="U3" s="69"/>
+      <c r="V3" s="69"/>
     </row>
     <row r="4" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="68" t="s">
+      <c r="A4" s="71" t="s">
         <v>70</v>
       </c>
-      <c r="B4" s="66"/>
-      <c r="C4" s="66"/>
-      <c r="D4" s="66"/>
-      <c r="E4" s="66"/>
-      <c r="F4" s="66"/>
-      <c r="G4" s="66"/>
-      <c r="H4" s="66"/>
-      <c r="I4" s="66"/>
-      <c r="J4" s="66"/>
-      <c r="K4" s="66"/>
-      <c r="L4" s="66"/>
-      <c r="M4" s="66"/>
-      <c r="N4" s="66"/>
-      <c r="O4" s="66"/>
-      <c r="P4" s="66"/>
-      <c r="Q4" s="66"/>
-      <c r="R4" s="66"/>
-      <c r="S4" s="66"/>
-      <c r="T4" s="66"/>
-      <c r="U4" s="66"/>
-      <c r="V4" s="66"/>
-      <c r="W4" s="66"/>
+      <c r="B4" s="69"/>
+      <c r="C4" s="69"/>
+      <c r="D4" s="69"/>
+      <c r="E4" s="69"/>
+      <c r="F4" s="69"/>
+      <c r="G4" s="69"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="69"/>
+      <c r="J4" s="69"/>
+      <c r="K4" s="69"/>
+      <c r="L4" s="69"/>
+      <c r="M4" s="69"/>
+      <c r="N4" s="69"/>
+      <c r="O4" s="69"/>
+      <c r="P4" s="69"/>
+      <c r="Q4" s="69"/>
+      <c r="R4" s="69"/>
+      <c r="S4" s="69"/>
+      <c r="T4" s="69"/>
+      <c r="U4" s="69"/>
+      <c r="V4" s="69"/>
+      <c r="W4" s="69"/>
     </row>
     <row r="5" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="68" t="s">
+      <c r="A5" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="66"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="66"/>
-      <c r="I5" s="66"/>
-      <c r="J5" s="66"/>
-      <c r="K5" s="66"/>
-      <c r="L5" s="66"/>
-      <c r="M5" s="66"/>
-      <c r="N5" s="66"/>
-      <c r="O5" s="66"/>
-      <c r="P5" s="66"/>
-      <c r="Q5" s="66"/>
-      <c r="R5" s="66"/>
-      <c r="S5" s="66"/>
-      <c r="T5" s="66"/>
-      <c r="U5" s="66"/>
-      <c r="V5" s="66"/>
+      <c r="B5" s="69"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
+      <c r="J5" s="69"/>
+      <c r="K5" s="69"/>
+      <c r="L5" s="69"/>
+      <c r="M5" s="69"/>
+      <c r="N5" s="69"/>
+      <c r="O5" s="69"/>
+      <c r="P5" s="69"/>
+      <c r="Q5" s="69"/>
+      <c r="R5" s="69"/>
+      <c r="S5" s="69"/>
+      <c r="T5" s="69"/>
+      <c r="U5" s="69"/>
+      <c r="V5" s="69"/>
     </row>
     <row r="6" spans="1:23" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="35" t="s">
@@ -3895,135 +3997,135 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="66"/>
-      <c r="H1" s="66"/>
-      <c r="I1" s="66"/>
-      <c r="J1" s="66"/>
-      <c r="K1" s="66"/>
-      <c r="L1" s="66"/>
-      <c r="M1" s="66"/>
-      <c r="N1" s="66"/>
-      <c r="O1" s="66"/>
-      <c r="P1" s="66"/>
-      <c r="Q1" s="66"/>
-      <c r="R1" s="66"/>
-      <c r="S1" s="66"/>
-      <c r="T1" s="66"/>
-      <c r="U1" s="66"/>
-      <c r="V1" s="66"/>
+      <c r="A1" s="68" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="69"/>
+      <c r="I1" s="69"/>
+      <c r="J1" s="69"/>
+      <c r="K1" s="69"/>
+      <c r="L1" s="69"/>
+      <c r="M1" s="69"/>
+      <c r="N1" s="69"/>
+      <c r="O1" s="69"/>
+      <c r="P1" s="69"/>
+      <c r="Q1" s="69"/>
+      <c r="R1" s="69"/>
+      <c r="S1" s="69"/>
+      <c r="T1" s="69"/>
+      <c r="U1" s="69"/>
+      <c r="V1" s="69"/>
     </row>
     <row r="2" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="67" t="s">
+      <c r="A2" s="70" t="s">
         <v>288</v>
       </c>
-      <c r="B2" s="66"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="66"/>
-      <c r="H2" s="66"/>
-      <c r="I2" s="66"/>
-      <c r="J2" s="66"/>
-      <c r="K2" s="66"/>
-      <c r="L2" s="66"/>
-      <c r="M2" s="66"/>
-      <c r="N2" s="66"/>
-      <c r="O2" s="66"/>
-      <c r="P2" s="66"/>
-      <c r="Q2" s="66"/>
-      <c r="R2" s="66"/>
-      <c r="S2" s="66"/>
-      <c r="T2" s="66"/>
-      <c r="U2" s="66"/>
-      <c r="V2" s="66"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="69"/>
+      <c r="L2" s="69"/>
+      <c r="M2" s="69"/>
+      <c r="N2" s="69"/>
+      <c r="O2" s="69"/>
+      <c r="P2" s="69"/>
+      <c r="Q2" s="69"/>
+      <c r="R2" s="69"/>
+      <c r="S2" s="69"/>
+      <c r="T2" s="69"/>
+      <c r="U2" s="69"/>
+      <c r="V2" s="69"/>
     </row>
     <row r="3" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="68" t="s">
+      <c r="A3" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="66"/>
-      <c r="C3" s="66"/>
-      <c r="D3" s="66"/>
-      <c r="E3" s="66"/>
-      <c r="F3" s="66"/>
-      <c r="G3" s="66"/>
-      <c r="H3" s="66"/>
-      <c r="I3" s="66"/>
-      <c r="J3" s="66"/>
-      <c r="K3" s="66"/>
-      <c r="L3" s="66"/>
-      <c r="M3" s="66"/>
-      <c r="N3" s="66"/>
-      <c r="O3" s="66"/>
-      <c r="P3" s="66"/>
-      <c r="Q3" s="66"/>
-      <c r="R3" s="66"/>
-      <c r="S3" s="66"/>
-      <c r="T3" s="66"/>
-      <c r="U3" s="66"/>
-      <c r="V3" s="66"/>
+      <c r="B3" s="69"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="69"/>
+      <c r="F3" s="69"/>
+      <c r="G3" s="69"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="69"/>
+      <c r="J3" s="69"/>
+      <c r="K3" s="69"/>
+      <c r="L3" s="69"/>
+      <c r="M3" s="69"/>
+      <c r="N3" s="69"/>
+      <c r="O3" s="69"/>
+      <c r="P3" s="69"/>
+      <c r="Q3" s="69"/>
+      <c r="R3" s="69"/>
+      <c r="S3" s="69"/>
+      <c r="T3" s="69"/>
+      <c r="U3" s="69"/>
+      <c r="V3" s="69"/>
     </row>
     <row r="4" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="68" t="s">
+      <c r="A4" s="71" t="s">
         <v>70</v>
       </c>
-      <c r="B4" s="66"/>
-      <c r="C4" s="66"/>
-      <c r="D4" s="66"/>
-      <c r="E4" s="66"/>
-      <c r="F4" s="66"/>
-      <c r="G4" s="66"/>
-      <c r="H4" s="66"/>
-      <c r="I4" s="66"/>
-      <c r="J4" s="66"/>
-      <c r="K4" s="66"/>
-      <c r="L4" s="66"/>
-      <c r="M4" s="66"/>
-      <c r="N4" s="66"/>
-      <c r="O4" s="66"/>
-      <c r="P4" s="66"/>
-      <c r="Q4" s="66"/>
-      <c r="R4" s="66"/>
-      <c r="S4" s="66"/>
-      <c r="T4" s="66"/>
-      <c r="U4" s="66"/>
-      <c r="V4" s="66"/>
-      <c r="W4" s="66"/>
+      <c r="B4" s="69"/>
+      <c r="C4" s="69"/>
+      <c r="D4" s="69"/>
+      <c r="E4" s="69"/>
+      <c r="F4" s="69"/>
+      <c r="G4" s="69"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="69"/>
+      <c r="J4" s="69"/>
+      <c r="K4" s="69"/>
+      <c r="L4" s="69"/>
+      <c r="M4" s="69"/>
+      <c r="N4" s="69"/>
+      <c r="O4" s="69"/>
+      <c r="P4" s="69"/>
+      <c r="Q4" s="69"/>
+      <c r="R4" s="69"/>
+      <c r="S4" s="69"/>
+      <c r="T4" s="69"/>
+      <c r="U4" s="69"/>
+      <c r="V4" s="69"/>
+      <c r="W4" s="69"/>
     </row>
     <row r="5" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="68" t="s">
+      <c r="A5" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="66"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="66"/>
-      <c r="I5" s="66"/>
-      <c r="J5" s="66"/>
-      <c r="K5" s="66"/>
-      <c r="L5" s="66"/>
-      <c r="M5" s="66"/>
-      <c r="N5" s="66"/>
-      <c r="O5" s="66"/>
-      <c r="P5" s="66"/>
-      <c r="Q5" s="66"/>
-      <c r="R5" s="66"/>
-      <c r="S5" s="66"/>
-      <c r="T5" s="66"/>
-      <c r="U5" s="66"/>
-      <c r="V5" s="66"/>
+      <c r="B5" s="69"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
+      <c r="J5" s="69"/>
+      <c r="K5" s="69"/>
+      <c r="L5" s="69"/>
+      <c r="M5" s="69"/>
+      <c r="N5" s="69"/>
+      <c r="O5" s="69"/>
+      <c r="P5" s="69"/>
+      <c r="Q5" s="69"/>
+      <c r="R5" s="69"/>
+      <c r="S5" s="69"/>
+      <c r="T5" s="69"/>
+      <c r="U5" s="69"/>
+      <c r="V5" s="69"/>
     </row>
     <row r="6" spans="1:23" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="35" t="s">
